--- a/docs/EE_Summary.xlsx
+++ b/docs/EE_Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\src\github\upulgun.github.io\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/374644a6aeffffba/Teaching/2026 Autumn/UG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D431A6E-B6E1-4DCD-B1A0-C80315C468F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="8_{C5959E4F-51F9-4286-83E1-FC9AEA47468E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B57E22AA-05A5-45BD-9DA7-CA75193BF603}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21705" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3825" yWindow="795" windowWidth="24435" windowHeight="16095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EE UG Subjects" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="196">
   <si>
     <t>ELEC 2001</t>
   </si>
@@ -356,9 +356,6 @@
   </si>
   <si>
     <t>ELEC2001</t>
-  </si>
-  <si>
-    <t>ELEC011 or MECH3004</t>
   </si>
   <si>
     <r>
@@ -561,9 +558,6 @@
   </si>
   <si>
     <t>Advanced Biomedical Electronics</t>
-  </si>
-  <si>
-    <t>Qi Cheng/ Ali Mehrabi</t>
   </si>
   <si>
     <t>ENGR 3029</t>
@@ -709,6 +703,9 @@
   </si>
   <si>
     <t>Qi Cheng</t>
+  </si>
+  <si>
+    <t>ELEC2011 or MECH3004</t>
   </si>
 </sst>
 </file>
@@ -845,11 +842,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1131,6 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1148,12 +1146,12 @@
         <v>83</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="12"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="2" t="s">
         <v>84</v>
       </c>
@@ -1172,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>79</v>
@@ -1181,10 +1179,10 @@
         <v>80</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G2" t="s">
         <v>93</v>
@@ -1195,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>81</v>
@@ -1218,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>50</v>
@@ -1230,7 +1228,7 @@
         <v>9</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G4" t="s">
         <v>93</v>
@@ -1241,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>52</v>
@@ -1253,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G5" t="s">
         <v>93</v>
@@ -1264,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>54</v>
@@ -1276,7 +1274,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G6" t="s">
         <v>93</v>
@@ -1287,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>71</v>
@@ -1299,10 +1297,10 @@
         <v>62</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1310,7 +1308,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>73</v>
@@ -1322,7 +1320,7 @@
         <v>62</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G8" t="s">
         <v>85</v>
@@ -1333,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>69</v>
@@ -1345,7 +1343,7 @@
         <v>62</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G9" t="s">
         <v>93</v>
@@ -1356,7 +1354,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>75</v>
@@ -1368,7 +1366,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G10" t="s">
         <v>93</v>
@@ -1379,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1387,7 +1385,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>77</v>
@@ -1399,7 +1397,7 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>163</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s">
         <v>93</v>
@@ -1410,7 +1408,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>0</v>
@@ -1433,7 +1431,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>4</v>
@@ -1456,7 +1454,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>7</v>
@@ -1479,10 +1477,10 @@
         <v>2</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
@@ -1491,13 +1489,13 @@
         <v>9</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1505,7 +1503,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>14</v>
@@ -1516,8 +1514,8 @@
       <c r="E17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="14" t="s">
-        <v>196</v>
+      <c r="F17" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="G17" t="s">
         <v>99</v>
@@ -1528,7 +1526,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>16</v>
@@ -1551,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>33</v>
@@ -1563,7 +1561,7 @@
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="G19" t="s">
         <v>104</v>
@@ -1574,7 +1572,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>58</v>
@@ -1589,7 +1587,7 @@
         <v>95</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1600,19 +1598,19 @@
         <v>3691</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1623,19 +1621,19 @@
         <v>3691</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G22" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1643,7 +1641,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1651,7 +1649,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>11</v>
@@ -1674,7 +1672,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>18</v>
@@ -1697,7 +1695,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>20</v>
@@ -1720,7 +1718,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>22</v>
@@ -1743,7 +1741,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>24</v>
@@ -1766,7 +1764,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>27</v>
@@ -1800,7 +1798,7 @@
       <c r="E30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="12" t="s">
         <v>91</v>
       </c>
       <c r="G30" t="s">
@@ -1815,19 +1813,19 @@
         <v>3691</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D31" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1838,19 +1836,19 @@
         <v>3691</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G32" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1858,13 +1856,13 @@
         <v>3</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D33" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>62</v>
@@ -1873,7 +1871,7 @@
         <v>6</v>
       </c>
       <c r="G33" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1881,7 +1879,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>56</v>
@@ -1907,7 +1905,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>60</v>
@@ -1916,21 +1914,21 @@
         <v>61</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G36" t="s">
         <v>93</v>
       </c>
       <c r="H36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -1938,7 +1936,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>35</v>
@@ -1953,7 +1951,7 @@
         <v>91</v>
       </c>
       <c r="G38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1961,7 +1959,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>37</v>
@@ -1973,10 +1971,10 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -1984,7 +1982,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>39</v>
@@ -1999,7 +1997,7 @@
         <v>96</v>
       </c>
       <c r="G40" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -2007,7 +2005,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>41</v>
@@ -2022,7 +2020,7 @@
         <v>10</v>
       </c>
       <c r="G41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -2030,7 +2028,7 @@
         <v>4</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>43</v>
@@ -2042,10 +2040,10 @@
         <v>9</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G42" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -2053,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>45</v>
@@ -2068,7 +2066,7 @@
         <v>96</v>
       </c>
       <c r="G43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -2091,7 +2089,7 @@
         <v>91</v>
       </c>
       <c r="G44" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2099,7 +2097,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>49</v>
@@ -2122,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>63</v>
@@ -2137,7 +2135,7 @@
         <v>94</v>
       </c>
       <c r="G46" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -2145,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>65</v>
@@ -2157,10 +2155,10 @@
         <v>62</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G47" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -2168,7 +2166,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>67</v>
@@ -2180,10 +2178,10 @@
         <v>62</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2194,19 +2192,19 @@
         <v>3771</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D49" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G49" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2217,19 +2215,19 @@
         <v>3771</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D50" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G50" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2260,7 +2258,7 @@
     <hyperlink ref="C22" r:id="rId10" tooltip="ENGR 3030" display="https://hbook.westernsydney.edu.au/search/?P=ENGR%203030" xr:uid="{D6FD8F43-5CF4-4303-9011-95D9CED216B0}"/>
     <hyperlink ref="C13" r:id="rId11" tooltip="ELEC 2001" display="https://hbook.westernsydney.edu.au/search/?P=ELEC%202001" xr:uid="{4CE1031C-CC9E-4494-A3B8-56A3EE97578D}"/>
     <hyperlink ref="C20" r:id="rId12" tooltip="ENGR 3006" display="https://hbook.westernsydney.edu.au/search/?P=ENGR%203006" xr:uid="{3C49E641-2AA6-4496-BE77-7FAC2CE50E55}"/>
-    <hyperlink ref="C18" r:id="rId13" tooltip="ELEC 2011" display="https://hbook.westernsydney.edu.au/search/?P=ELEC%202011" xr:uid="{D085E05D-06A1-4EDE-88F3-D2F8BC7E9C3E}"/>
+    <hyperlink ref="C18" r:id="rId13" tooltip="ELEC 2011" xr:uid="{D085E05D-06A1-4EDE-88F3-D2F8BC7E9C3E}"/>
     <hyperlink ref="C19" r:id="rId14" tooltip="ELEC 3011" display="https://hbook.westernsydney.edu.au/search/?P=ELEC%203011" xr:uid="{173E7C5B-A2D5-4CD6-B086-87026B9F1A11}"/>
     <hyperlink ref="C12" r:id="rId15" tooltip="ELEC 1001" display="https://hbook.westernsydney.edu.au/search/?P=ELEC%201001" xr:uid="{372A0116-2D3F-4061-AF9A-E7427ED27AF5}"/>
     <hyperlink ref="C31" r:id="rId16" tooltip="ENGR 3013" display="https://hbook.westernsydney.edu.au/search/?P=ENGR%203013" xr:uid="{531F7A62-AE7A-4802-9F81-A27CAAA6EB65}"/>
@@ -2299,6 +2297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F59BBB39-4893-4D7C-937C-DD64A9CC86E4}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2311,12 +2310,12 @@
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="12"/>
+      <c r="C1" s="14"/>
       <c r="D1" s="2" t="s">
         <v>84</v>
       </c>
@@ -2326,13 +2325,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" t="s">
         <v>128</v>
-      </c>
-      <c r="C2" t="s">
-        <v>129</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>9</v>
@@ -2343,13 +2342,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" t="s">
         <v>145</v>
-      </c>
-      <c r="C3" t="s">
-        <v>146</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
@@ -2360,13 +2359,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" t="s">
         <v>130</v>
-      </c>
-      <c r="C4" t="s">
-        <v>131</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
@@ -2377,13 +2376,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" t="s">
         <v>132</v>
-      </c>
-      <c r="C5" t="s">
-        <v>133</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>2</v>
@@ -2394,13 +2393,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" t="s">
         <v>134</v>
-      </c>
-      <c r="C6" t="s">
-        <v>135</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
@@ -2411,13 +2410,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="C7" t="s">
         <v>137</v>
-      </c>
-      <c r="C7" t="s">
-        <v>138</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>2</v>
@@ -2428,13 +2427,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" t="s">
         <v>139</v>
-      </c>
-      <c r="C8" t="s">
-        <v>140</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>9</v>
@@ -2445,13 +2444,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" t="s">
         <v>141</v>
-      </c>
-      <c r="C9" t="s">
-        <v>142</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>2</v>
@@ -2462,18 +2461,18 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
         <v>143</v>
-      </c>
-      <c r="C10" t="s">
-        <v>144</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2482,64 +2481,64 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" t="s">
         <v>156</v>
       </c>
-      <c r="C12" t="s">
-        <v>157</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
         <v>122</v>
       </c>
-      <c r="C14" t="s">
-        <v>123</v>
-      </c>
       <c r="D14" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" t="s">
         <v>150</v>
-      </c>
-      <c r="C15" t="s">
-        <v>151</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>2</v>
@@ -2550,24 +2549,24 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" t="s">
         <v>161</v>
-      </c>
-      <c r="C16" t="s">
-        <v>162</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" t="s">
         <v>159</v>
-      </c>
-      <c r="C17" t="s">
-        <v>160</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>32</v>
@@ -2578,36 +2577,36 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" t="s">
         <v>154</v>
       </c>
-      <c r="C18" t="s">
-        <v>155</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" t="s">
         <v>152</v>
       </c>
-      <c r="C19" t="s">
-        <v>153</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2615,36 +2614,36 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" t="s">
         <v>124</v>
-      </c>
-      <c r="C21" t="s">
-        <v>125</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" t="s">
         <v>147</v>
-      </c>
-      <c r="C22" t="s">
-        <v>148</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
